--- a/Luban/DataTables/Datas/Icon.xlsx
+++ b/Luban/DataTables/Datas/Icon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="8700"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -80,22 +80,28 @@
     <t>shop1</t>
   </si>
   <si>
+    <t>player0</t>
+  </si>
+  <si>
+    <t>player1</t>
+  </si>
+  <si>
+    <t>game0</t>
+  </si>
+  <si>
+    <t>game1</t>
+  </si>
+  <si>
+    <t>event0</t>
+  </si>
+  <si>
+    <t>event1</t>
+  </si>
+  <si>
     <t>setting0</t>
   </si>
   <si>
     <t>setting1</t>
-  </si>
-  <si>
-    <t>game0</t>
-  </si>
-  <si>
-    <t>game1</t>
-  </si>
-  <si>
-    <t>player0</t>
-  </si>
-  <si>
-    <t>player1</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
@@ -1119,7 +1125,6 @@
       <c r="B5" s="1">
         <v>1001</v>
       </c>
-      <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1131,7 +1136,6 @@
       <c r="B6" s="1">
         <v>1002</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,6 +1207,28 @@
       </c>
       <c r="E12" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/Icon.xlsx
+++ b/Luban/DataTables/Datas/Icon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowWidth="26880" windowHeight="9285"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>14</v>

--- a/Luban/DataTables/Datas/Icon.xlsx
+++ b/Luban/DataTables/Datas/Icon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -62,13 +62,73 @@
     <t>##</t>
   </si>
   <si>
-    <t>数据</t>
+    <t>备注</t>
   </si>
   <si>
     <t>图集</t>
   </si>
   <si>
     <t>图标</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>ui_res_lv</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>ui_res_exp</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>ui_res_coin</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>ui_res_gem</t>
+  </si>
+  <si>
+    <t>花1</t>
+  </si>
+  <si>
+    <t>ui_res_flower1</t>
+  </si>
+  <si>
+    <t>花2</t>
+  </si>
+  <si>
+    <t>ui_res_flower2</t>
+  </si>
+  <si>
+    <t>叶</t>
+  </si>
+  <si>
+    <t>ui_res_leaf</t>
+  </si>
+  <si>
+    <t>星1</t>
+  </si>
+  <si>
+    <t>ui_res_star1</t>
+  </si>
+  <si>
+    <t>星2</t>
+  </si>
+  <si>
+    <t>ui_res_star2</t>
   </si>
   <si>
     <t>HomeTabBar</t>
@@ -123,6 +183,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -233,13 +300,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -276,6 +336,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -295,12 +361,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,55 +647,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,8 +777,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1043,13 +1106,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="20.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.375" style="2" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1057,16 +1120,16 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1074,16 +1137,16 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1091,21 +1154,21 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1121,116 +1184,261 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="1">
+    <row r="5" spans="2:3">
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="2">
         <v>1001</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="1">
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="2">
         <v>1002</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="1">
-        <v>1003</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="1">
-        <v>1004</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="1">
-        <v>1005</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
+      <c r="B9" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="1">
-        <v>1006</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
+      <c r="B10" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="1">
-        <v>1007</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
+      <c r="B11" s="2">
+        <v>1012</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="1">
-        <v>1008</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>22</v>
+      <c r="B12" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="1">
-        <v>1009</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>23</v>
+      <c r="B13" s="2">
+        <v>1014</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="1">
-        <v>1010</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
+      <c r="B14" s="2">
+        <v>1015</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="2">
+        <v>1016</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2">
+        <v>100001</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="2">
+        <v>100002</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="2">
+        <v>100003</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="2">
+        <v>100004</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="2">
+        <v>100005</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="2">
+        <v>100006</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2">
+        <v>100007</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2">
+        <v>100008</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2">
+        <v>100009</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2">
+        <v>100010</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/Icon.xlsx
+++ b/Luban/DataTables/Datas/Icon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,45 @@
   </si>
   <si>
     <t>ui_res_star2</t>
+  </si>
+  <si>
+    <t>礼包1</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>GemPackIcon_300</t>
+  </si>
+  <si>
+    <t>礼包2</t>
+  </si>
+  <si>
+    <t>GemPackIcon_680</t>
+  </si>
+  <si>
+    <t>礼包3</t>
+  </si>
+  <si>
+    <t>GemPackIcon_1280</t>
+  </si>
+  <si>
+    <t>礼包4</t>
+  </si>
+  <si>
+    <t>GemPackIcon_1980</t>
+  </si>
+  <si>
+    <t>礼包5</t>
+  </si>
+  <si>
+    <t>GemPackIcon_3280</t>
+  </si>
+  <si>
+    <t>礼包6</t>
+  </si>
+  <si>
+    <t>GemPackIcon_6480</t>
   </si>
   <si>
     <t>HomeTabBar</t>
@@ -1106,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
@@ -1323,28 +1362,25 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:1">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="2">
-        <v>100001</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>35</v>
+    <row r="17" s="1" customFormat="1" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="2">
-        <v>100002</v>
+        <v>10001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>36</v>
@@ -1352,93 +1388,195 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="2">
-        <v>100003</v>
+        <v>10002</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="2">
-        <v>100004</v>
+        <v>10003</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="2">
-        <v>100005</v>
+        <v>10004</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="2">
-        <v>100006</v>
+        <v>10005</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="2">
-        <v>100007</v>
+        <v>10006</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="2">
-        <v>100008</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="2">
-        <v>100009</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="2">
+        <v>100001</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="2">
+        <v>100002</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="2">
+        <v>100003</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="2">
+        <v>100004</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="2">
+        <v>100005</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="2">
+        <v>100006</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="2">
+        <v>100007</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="2">
+        <v>100008</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="2">
+        <v>100009</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="2">
         <v>100010</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1"/>
+      <c r="D35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
